--- a/pds_admin_Punjab_R/Backend/Backend/Tagging_Sheet_With_WB.xlsx
+++ b/pds_admin_Punjab_R/Backend/Backend/Tagging_Sheet_With_WB.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V89"/>
+  <dimension ref="A1:V84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,36 +558,36 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>JALANDHAR</t>
+          <t>AMRITSAR</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ADAMPUR</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1046</v>
+        <v>3</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADAMPUR  </t>
+          <t>CHAK SAKANDAR GRAIN MARKET</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>31.425406</v>
+        <v>31.84430551</v>
       </c>
       <c r="I2" t="n">
-        <v>75.719528</v>
+        <v>74.91208039999999</v>
       </c>
       <c r="J2" t="n">
-        <v>522</v>
+        <v>393</v>
       </c>
       <c r="K2" t="n">
-        <v>31.4204409</v>
+        <v>31.863261</v>
       </c>
       <c r="L2" t="n">
-        <v>75.69994199999999</v>
+        <v>74.945286</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>625</v>
+        <v>3</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -609,19 +609,19 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>JALANDHAR</t>
+          <t>AMRITSAR</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>ADAMPUR</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>31.408658</v>
+        <v>31.8529346</v>
       </c>
       <c r="T2" t="n">
-        <v>75.685958</v>
+        <v>74.91584450000001</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>21500</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="3">
@@ -650,36 +650,36 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>AMRITSAR</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>501</v>
+        <v>23</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ABOHAR GRAIN MARKET</t>
+          <t>BHILOWAL GRAIN MARKET</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>30.156605</v>
+        <v>31.7398221</v>
       </c>
       <c r="I3" t="n">
-        <v>74.19572100000001</v>
+        <v>74.6072853</v>
       </c>
       <c r="J3" t="n">
-        <v>280</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>30.154922</v>
+        <v>31.781936</v>
       </c>
       <c r="L3" t="n">
-        <v>74.193507</v>
+        <v>74.76758049999999</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>396</v>
+        <v>5</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -701,19 +701,19 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>AMRITSAR</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>30.15881226</v>
+        <v>31.800077</v>
       </c>
       <c r="T3" t="n">
-        <v>74.18214294000001</v>
+        <v>74.588493</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>90000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="4">
@@ -747,7 +747,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -765,13 +765,13 @@
         <v>74.19572100000001</v>
       </c>
       <c r="J4" t="n">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="K4" t="n">
-        <v>30.15894356</v>
+        <v>30.154922</v>
       </c>
       <c r="L4" t="n">
-        <v>74.18094151</v>
+        <v>74.193507</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -798,14 +798,14 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>30.15894356</v>
+        <v>30.15881226</v>
       </c>
       <c r="T4" t="n">
-        <v>74.18094151</v>
+        <v>74.18214294000001</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>60000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="5">
@@ -839,7 +839,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -871,7 +871,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -890,14 +890,14 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>30.15848535</v>
+        <v>30.15894356</v>
       </c>
       <c r="T5" t="n">
-        <v>74.18085842000001</v>
+        <v>74.18094151</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>120000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="6">
@@ -931,7 +931,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -982,14 +982,14 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>30.15809938</v>
+        <v>30.15848535</v>
       </c>
       <c r="T6" t="n">
-        <v>74.16401603</v>
+        <v>74.18085842000001</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>145397</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="7">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1041,13 +1041,13 @@
         <v>74.19572100000001</v>
       </c>
       <c r="J7" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="K7" t="n">
-        <v>30.163017</v>
+        <v>30.15894356</v>
       </c>
       <c r="L7" t="n">
-        <v>74.186234</v>
+        <v>74.18094151</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1074,14 +1074,14 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>30.1689126</v>
+        <v>30.15809938</v>
       </c>
       <c r="T7" t="n">
-        <v>74.183232</v>
+        <v>74.16401603</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>31477</v>
+        <v>33610</v>
       </c>
     </row>
     <row r="8">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S8" t="n">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>BAHADUR KHERA GRAIN MARKET</t>
+          <t>ABOHAR GRAIN MARKET</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>30.099748</v>
+        <v>30.156605</v>
       </c>
       <c r="I9" t="n">
-        <v>74.34759699999999</v>
+        <v>74.19572100000001</v>
       </c>
       <c r="J9" t="n">
         <v>287</v>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S9" t="n">
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>71835.5</v>
+        <v>143264</v>
       </c>
     </row>
     <row r="10">
@@ -1299,31 +1299,31 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>BAHAAW WALA GRAIN MARKET</t>
+          <t>BAHADUR KHERA GRAIN MARKET</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>30.028699</v>
+        <v>30.099748</v>
       </c>
       <c r="I10" t="n">
-        <v>74.197309</v>
+        <v>74.34759699999999</v>
       </c>
       <c r="J10" t="n">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="K10" t="n">
-        <v>30.105887</v>
+        <v>30.090357</v>
       </c>
       <c r="L10" t="n">
-        <v>74.18092900000001</v>
+        <v>74.20853700000001</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1350,14 +1350,14 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>30.10552983</v>
+        <v>30.08793156</v>
       </c>
       <c r="T10" t="n">
-        <v>74.18014506</v>
+        <v>74.20908439</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>73538.5</v>
+        <v>48247.5</v>
       </c>
     </row>
     <row r="11">
@@ -1391,31 +1391,31 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>BAHAAW WALA GRAIN MARKET</t>
+          <t>BAHADUR KHERA GRAIN MARKET</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>30.028699</v>
+        <v>30.099748</v>
       </c>
       <c r="I11" t="n">
-        <v>74.197309</v>
+        <v>74.34759699999999</v>
       </c>
       <c r="J11" t="n">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="K11" t="n">
-        <v>30.126927</v>
+        <v>30.100105</v>
       </c>
       <c r="L11" t="n">
-        <v>74.161942</v>
+        <v>74.20670699999999</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1442,14 +1442,14 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>30.126927</v>
+        <v>30.0974593</v>
       </c>
       <c r="T11" t="n">
-        <v>74.161942</v>
+        <v>74.206666</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>322</v>
+        <v>23588</v>
       </c>
     </row>
     <row r="12">
@@ -1483,31 +1483,31 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>BUKENWALA GRAIN MARKET</t>
+          <t>BAHAAW WALA GRAIN MARKET</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>30.162859</v>
+        <v>30.028699</v>
       </c>
       <c r="I12" t="n">
-        <v>73.991192</v>
+        <v>74.197309</v>
       </c>
       <c r="J12" t="n">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="K12" t="n">
-        <v>30.126927</v>
+        <v>30.105887</v>
       </c>
       <c r="L12" t="n">
-        <v>74.161942</v>
+        <v>74.18092900000001</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1534,14 +1534,14 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>30.126927</v>
+        <v>30.10552983</v>
       </c>
       <c r="T12" t="n">
-        <v>74.161942</v>
+        <v>74.18014506</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>37309</v>
+        <v>73860.5</v>
       </c>
     </row>
     <row r="13">
@@ -1575,31 +1575,31 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>BALLUANA GRAIN MARKET</t>
+          <t>BUKENWALA GRAIN MARKET</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>30.16948</v>
+        <v>30.162859</v>
       </c>
       <c r="I13" t="n">
-        <v>74.28432100000001</v>
+        <v>73.991192</v>
       </c>
       <c r="J13" t="n">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="K13" t="n">
-        <v>30.163017</v>
+        <v>30.126927</v>
       </c>
       <c r="L13" t="n">
-        <v>74.186234</v>
+        <v>74.161942</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1626,14 +1626,14 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S13" t="n">
-        <v>30.1689126</v>
+        <v>30.126927</v>
       </c>
       <c r="T13" t="n">
-        <v>74.183232</v>
+        <v>74.161942</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>2823</v>
+        <v>37309</v>
       </c>
     </row>
     <row r="14">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1685,13 +1685,13 @@
         <v>74.28432100000001</v>
       </c>
       <c r="J14" t="n">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="K14" t="n">
-        <v>30.163017</v>
+        <v>30.126927</v>
       </c>
       <c r="L14" t="n">
-        <v>74.186234</v>
+        <v>74.161942</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1718,14 +1718,14 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S14" t="n">
-        <v>30.16991135</v>
+        <v>30.126927</v>
       </c>
       <c r="T14" t="n">
-        <v>74.18230296</v>
+        <v>74.161942</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>15202.5</v>
+        <v>18025.5</v>
       </c>
     </row>
     <row r="15">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1810,14 +1810,14 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S15" t="n">
-        <v>30.08675444</v>
+        <v>30.08793156</v>
       </c>
       <c r="T15" t="n">
-        <v>74.20888524</v>
+        <v>74.20908439</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>49766</v>
+        <v>16177.5</v>
       </c>
     </row>
     <row r="16">
@@ -1851,31 +1851,31 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CHANNAN KHERA GRAIN MARKET</t>
+          <t>BHAAGU GRAIN MARKET</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>30.182524</v>
+        <v>30.034436</v>
       </c>
       <c r="I16" t="n">
-        <v>74.326095</v>
+        <v>74.233859</v>
       </c>
       <c r="J16" t="n">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="K16" t="n">
-        <v>30.163017</v>
+        <v>30.090357</v>
       </c>
       <c r="L16" t="n">
-        <v>74.186234</v>
+        <v>74.20853700000001</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1902,14 +1902,14 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S16" t="n">
-        <v>30.16991135</v>
+        <v>30.08675444</v>
       </c>
       <c r="T16" t="n">
-        <v>74.18230296</v>
+        <v>74.20888524</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>41707.5</v>
+        <v>33588.5</v>
       </c>
     </row>
     <row r="17">
@@ -1943,31 +1943,31 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>CHURHI WALA DHANNA GRAIN MARKET</t>
+          <t>CHANNAN KHERA GRAIN MARKET</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>30.199756</v>
+        <v>30.182524</v>
       </c>
       <c r="I17" t="n">
-        <v>74.108656</v>
+        <v>74.326095</v>
       </c>
       <c r="J17" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="K17" t="n">
-        <v>30.180346</v>
+        <v>30.163017</v>
       </c>
       <c r="L17" t="n">
-        <v>74.17439299999999</v>
+        <v>74.186234</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1994,14 +1994,14 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S17" t="n">
-        <v>30.15809938</v>
+        <v>30.1689126</v>
       </c>
       <c r="T17" t="n">
-        <v>74.16401603</v>
+        <v>74.183232</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>18038</v>
+        <v>13129</v>
       </c>
     </row>
     <row r="18">
@@ -2035,22 +2035,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>DEEWAN KHERA GRAIN MARKET</t>
+          <t>CHANNAN KHERA GRAIN MARKET</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>30.113508</v>
+        <v>30.182524</v>
       </c>
       <c r="I18" t="n">
-        <v>73.989543</v>
+        <v>74.326095</v>
       </c>
       <c r="J18" t="n">
         <v>287</v>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S18" t="n">
@@ -2101,7 +2101,7 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>44568.5</v>
+        <v>28578.5</v>
       </c>
     </row>
     <row r="19">
@@ -2127,31 +2127,31 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>DHABA KOKARIYA GRAIN MARKET</t>
+          <t>CHURHI WALA DHANNA GRAIN MARKET</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>30.122605</v>
+        <v>30.199756</v>
       </c>
       <c r="I19" t="n">
-        <v>74.328892</v>
+        <v>74.108656</v>
       </c>
       <c r="J19" t="n">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="K19" t="n">
-        <v>30.126927</v>
+        <v>30.180346</v>
       </c>
       <c r="L19" t="n">
-        <v>74.161942</v>
+        <v>74.17439299999999</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -2178,14 +2178,14 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S19" t="n">
-        <v>30.126927</v>
+        <v>30.15809938</v>
       </c>
       <c r="T19" t="n">
-        <v>74.161942</v>
+        <v>74.16401603</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>25216</v>
+        <v>18038</v>
       </c>
     </row>
     <row r="20">
@@ -2219,31 +2219,31 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>DHARANGWALA GRAIN MARKET</t>
+          <t>DEEWAN KHERA GRAIN MARKET</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>30.237206</v>
+        <v>30.113508</v>
       </c>
       <c r="I20" t="n">
-        <v>74.23982700000001</v>
+        <v>73.989543</v>
       </c>
       <c r="J20" t="n">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="K20" t="n">
-        <v>30.175344</v>
+        <v>30.126927</v>
       </c>
       <c r="L20" t="n">
-        <v>74.178363</v>
+        <v>74.161942</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -2270,14 +2270,14 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S20" t="n">
-        <v>30.17081207</v>
+        <v>30.126927</v>
       </c>
       <c r="T20" t="n">
-        <v>74.18179719</v>
+        <v>74.161942</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>44802</v>
+        <v>44568.5</v>
       </c>
     </row>
     <row r="21">
@@ -2311,31 +2311,31 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>DHINGANWALI GRAIN MARKET</t>
+          <t>DHABA KOKARIYA GRAIN MARKET</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>30.023582</v>
+        <v>30.122605</v>
       </c>
       <c r="I21" t="n">
-        <v>74.04262799999999</v>
+        <v>74.328892</v>
       </c>
       <c r="J21" t="n">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="K21" t="n">
-        <v>30.126927</v>
+        <v>30.100105</v>
       </c>
       <c r="L21" t="n">
-        <v>74.161942</v>
+        <v>74.20670699999999</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -2362,14 +2362,14 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S21" t="n">
-        <v>30.126927</v>
+        <v>30.0974593</v>
       </c>
       <c r="T21" t="n">
-        <v>74.161942</v>
+        <v>74.206666</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>30276.5</v>
+        <v>25216</v>
       </c>
     </row>
     <row r="22">
@@ -2403,31 +2403,31 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>DODHEWALA GRAIN MARKET</t>
+          <t>DHARANGWALA GRAIN MARKET</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>29.960526</v>
+        <v>30.237206</v>
       </c>
       <c r="I22" t="n">
-        <v>74.219824</v>
+        <v>74.23982700000001</v>
       </c>
       <c r="J22" t="n">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="K22" t="n">
-        <v>30.105887</v>
+        <v>30.175344</v>
       </c>
       <c r="L22" t="n">
-        <v>74.18092900000001</v>
+        <v>74.178363</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -2454,14 +2454,14 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S22" t="n">
-        <v>30.10552983</v>
+        <v>30.17081207</v>
       </c>
       <c r="T22" t="n">
-        <v>74.18014506</v>
+        <v>74.18179719</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>19961.5</v>
+        <v>44802</v>
       </c>
     </row>
     <row r="23">
@@ -2495,31 +2495,31 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>DUTARANWALI GRAIN MARKET</t>
+          <t>DHINGANWALI GRAIN MARKET</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>30.082625</v>
+        <v>30.023582</v>
       </c>
       <c r="I23" t="n">
-        <v>74.288794</v>
+        <v>74.04262799999999</v>
       </c>
       <c r="J23" t="n">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="K23" t="n">
-        <v>30.100105</v>
+        <v>30.126927</v>
       </c>
       <c r="L23" t="n">
-        <v>74.20670699999999</v>
+        <v>74.161942</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -2546,14 +2546,14 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S23" t="n">
-        <v>30.0974593</v>
+        <v>30.126927</v>
       </c>
       <c r="T23" t="n">
-        <v>74.206666</v>
+        <v>74.161942</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>9709</v>
+        <v>30276.5</v>
       </c>
     </row>
     <row r="24">
@@ -2587,31 +2587,31 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>DUTARANWALI GRAIN MARKET</t>
+          <t>DODHEWALA GRAIN MARKET</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>30.082625</v>
+        <v>29.960526</v>
       </c>
       <c r="I24" t="n">
-        <v>74.288794</v>
+        <v>74.219824</v>
       </c>
       <c r="J24" t="n">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="K24" t="n">
-        <v>30.126927</v>
+        <v>30.090357</v>
       </c>
       <c r="L24" t="n">
-        <v>74.161942</v>
+        <v>74.20853700000001</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -2638,14 +2638,14 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S24" t="n">
-        <v>30.126927</v>
+        <v>30.08675444</v>
       </c>
       <c r="T24" t="n">
-        <v>74.161942</v>
+        <v>74.20888524</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>54672</v>
+        <v>19961.5</v>
       </c>
     </row>
     <row r="25">
@@ -2679,31 +2679,31 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>GADA DOB GRAIN MARKET</t>
+          <t>DUTARANWALI GRAIN MARKET</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>30.221432</v>
+        <v>30.082625</v>
       </c>
       <c r="I25" t="n">
-        <v>74.35153099999999</v>
+        <v>74.288794</v>
       </c>
       <c r="J25" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="K25" t="n">
-        <v>30.175344</v>
+        <v>30.090357</v>
       </c>
       <c r="L25" t="n">
-        <v>74.178363</v>
+        <v>74.20853700000001</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -2730,14 +2730,14 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S25" t="n">
-        <v>30.17081207</v>
+        <v>30.08793156</v>
       </c>
       <c r="T25" t="n">
-        <v>74.18179719</v>
+        <v>74.20908439</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>13755.5</v>
+        <v>64381</v>
       </c>
     </row>
     <row r="26">
@@ -2771,31 +2771,31 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>GADA DOB GRAIN MARKET</t>
+          <t>GHALLU GRAIN MARKET</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>30.221432</v>
+        <v>30.254598</v>
       </c>
       <c r="I26" t="n">
-        <v>74.35153099999999</v>
+        <v>74.124285</v>
       </c>
       <c r="J26" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K26" t="n">
-        <v>30.163017</v>
+        <v>30.180346</v>
       </c>
       <c r="L26" t="n">
-        <v>74.186234</v>
+        <v>74.17439299999999</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -2822,14 +2822,14 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S26" t="n">
-        <v>30.16991135</v>
+        <v>30.15809938</v>
       </c>
       <c r="T26" t="n">
-        <v>74.18230296</v>
+        <v>74.16401603</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>6714.5</v>
+        <v>39817.5</v>
       </c>
     </row>
     <row r="27">
@@ -2863,31 +2863,31 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>GHALLU GRAIN MARKET</t>
+          <t>GOBINDGARH GRAIN MARKET</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>30.254598</v>
+        <v>30.173582</v>
       </c>
       <c r="I27" t="n">
-        <v>74.124285</v>
+        <v>74.250483</v>
       </c>
       <c r="J27" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="K27" t="n">
-        <v>30.180346</v>
+        <v>30.163017</v>
       </c>
       <c r="L27" t="n">
-        <v>74.17439299999999</v>
+        <v>74.186234</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -2914,14 +2914,14 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S27" t="n">
-        <v>30.15809938</v>
+        <v>30.1689126</v>
       </c>
       <c r="T27" t="n">
-        <v>74.16401603</v>
+        <v>74.183232</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>39817.5</v>
+        <v>10375.5</v>
       </c>
     </row>
     <row r="28">
@@ -2955,31 +2955,31 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>GOBINDGARH GRAIN MARKET</t>
+          <t>JANDWALA MEERA SANGLA GRAIN MARKET</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>30.173582</v>
+        <v>30.21019</v>
       </c>
       <c r="I28" t="n">
-        <v>74.250483</v>
+        <v>74.024728</v>
       </c>
       <c r="J28" t="n">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="K28" t="n">
-        <v>30.163017</v>
+        <v>30.126927</v>
       </c>
       <c r="L28" t="n">
-        <v>74.186234</v>
+        <v>74.161942</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -3006,14 +3006,14 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S28" t="n">
-        <v>30.16991135</v>
+        <v>30.126927</v>
       </c>
       <c r="T28" t="n">
-        <v>74.18230296</v>
+        <v>74.161942</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>10375.5</v>
+        <v>100949.5</v>
       </c>
     </row>
     <row r="29">
@@ -3047,22 +3047,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>JANDWALA MEERA SANGLA GRAIN MARKET</t>
+          <t>JHUMIYANWALI GRAIN MARKET</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>30.21019</v>
+        <v>30.257887</v>
       </c>
       <c r="I29" t="n">
-        <v>74.024728</v>
+        <v>74.185624</v>
       </c>
       <c r="J29" t="n">
         <v>285</v>
@@ -3079,7 +3079,7 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -3098,14 +3098,14 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S29" t="n">
-        <v>30.15809938</v>
+        <v>30.17767461</v>
       </c>
       <c r="T29" t="n">
-        <v>74.16401603</v>
+        <v>74.17723581</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>72343</v>
+        <v>36622.5</v>
       </c>
     </row>
     <row r="30">
@@ -3139,31 +3139,31 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>JANDWALA MEERA SANGLA GRAIN MARKET</t>
+          <t>JHURAD KHERA GRAIN MARKET</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>30.21019</v>
+        <v>30.007285</v>
       </c>
       <c r="I30" t="n">
-        <v>74.024728</v>
+        <v>74.126166</v>
       </c>
       <c r="J30" t="n">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="K30" t="n">
-        <v>30.126927</v>
+        <v>30.105887</v>
       </c>
       <c r="L30" t="n">
-        <v>74.161942</v>
+        <v>74.18092900000001</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -3190,14 +3190,14 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S30" t="n">
-        <v>30.126927</v>
+        <v>30.10552983</v>
       </c>
       <c r="T30" t="n">
-        <v>74.161942</v>
+        <v>74.18014506</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>28606.5</v>
+        <v>11652.5</v>
       </c>
     </row>
     <row r="31">
@@ -3231,31 +3231,31 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>JHUMIYANWALI GRAIN MARKET</t>
+          <t>JHURAD KHERA GRAIN MARKET</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>30.257887</v>
+        <v>30.007285</v>
       </c>
       <c r="I31" t="n">
-        <v>74.185624</v>
+        <v>74.126166</v>
       </c>
       <c r="J31" t="n">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="K31" t="n">
-        <v>30.175344</v>
+        <v>30.126927</v>
       </c>
       <c r="L31" t="n">
-        <v>74.178363</v>
+        <v>74.161942</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -3282,14 +3282,14 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S31" t="n">
-        <v>30.17081207</v>
+        <v>30.126927</v>
       </c>
       <c r="T31" t="n">
-        <v>74.18179719</v>
+        <v>74.161942</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>2347.5</v>
+        <v>16592.5</v>
       </c>
     </row>
     <row r="32">
@@ -3323,31 +3323,31 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>JHUMIYANWALI GRAIN MARKET</t>
+          <t>KHUPAYA SARWAR GRAIN MARKET</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>30.257887</v>
+        <v>30.127701</v>
       </c>
       <c r="I32" t="n">
-        <v>74.185624</v>
+        <v>74.06368999999999</v>
       </c>
       <c r="J32" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K32" t="n">
-        <v>30.180346</v>
+        <v>30.126927</v>
       </c>
       <c r="L32" t="n">
-        <v>74.17439299999999</v>
+        <v>74.161942</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -3374,14 +3374,14 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S32" t="n">
-        <v>30.17767461</v>
+        <v>30.126927</v>
       </c>
       <c r="T32" t="n">
-        <v>74.17723581</v>
+        <v>74.161942</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>34275</v>
+        <v>21311</v>
       </c>
     </row>
     <row r="33">
@@ -3415,31 +3415,31 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>JHURAD KHERA GRAIN MARKET</t>
+          <t>KULAR GRAIN MARKET</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>30.007285</v>
+        <v>29.98347</v>
       </c>
       <c r="I33" t="n">
-        <v>74.126166</v>
+        <v>74.283652</v>
       </c>
       <c r="J33" t="n">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="K33" t="n">
-        <v>30.126927</v>
+        <v>30.090357</v>
       </c>
       <c r="L33" t="n">
-        <v>74.161942</v>
+        <v>74.20853700000001</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -3466,14 +3466,14 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S33" t="n">
-        <v>30.126927</v>
+        <v>30.08793156</v>
       </c>
       <c r="T33" t="n">
-        <v>74.161942</v>
+        <v>74.20908439</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>28245</v>
+        <v>34094</v>
       </c>
     </row>
     <row r="34">
@@ -3507,31 +3507,31 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>KALAR KHERA GRAIN MARKET</t>
+          <t>KUNDAL GRAIN MARKET</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>30.039412</v>
+        <v>30.216512</v>
       </c>
       <c r="I34" t="n">
-        <v>73.954567</v>
+        <v>74.269492</v>
       </c>
       <c r="J34" t="n">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="K34" t="n">
-        <v>30.126927</v>
+        <v>30.163017</v>
       </c>
       <c r="L34" t="n">
-        <v>74.161942</v>
+        <v>74.186234</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -3558,14 +3558,14 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S34" t="n">
-        <v>30.126927</v>
+        <v>30.1689126</v>
       </c>
       <c r="T34" t="n">
-        <v>74.161942</v>
+        <v>74.183232</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="V34" t="n">
-        <v>12854</v>
+        <v>10795.5</v>
       </c>
     </row>
     <row r="35">
@@ -3599,31 +3599,31 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>KHUMBAN GRAIN MARKET</t>
+          <t>KUNDAL GRAIN MARKET</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>30.012837</v>
+        <v>30.216512</v>
       </c>
       <c r="I35" t="n">
-        <v>74.432883</v>
+        <v>74.269492</v>
       </c>
       <c r="J35" t="n">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="K35" t="n">
-        <v>30.090357</v>
+        <v>30.175344</v>
       </c>
       <c r="L35" t="n">
-        <v>74.20853700000001</v>
+        <v>74.178363</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -3650,14 +3650,14 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S35" t="n">
-        <v>30.0974593</v>
+        <v>30.16991135</v>
       </c>
       <c r="T35" t="n">
-        <v>74.206666</v>
+        <v>74.18230296</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="V35" t="n">
-        <v>74081</v>
+        <v>21605.5</v>
       </c>
     </row>
     <row r="36">
@@ -3691,31 +3691,31 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>KHUPAYA SARWAR GRAIN MARKET</t>
+          <t>MALOOKPURA GRAIN MARKET</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>30.127701</v>
+        <v>30.132598</v>
       </c>
       <c r="I36" t="n">
-        <v>74.06368999999999</v>
+        <v>74.343463</v>
       </c>
       <c r="J36" t="n">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="K36" t="n">
-        <v>30.126927</v>
+        <v>30.100105</v>
       </c>
       <c r="L36" t="n">
-        <v>74.161942</v>
+        <v>74.20670699999999</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -3742,14 +3742,14 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S36" t="n">
-        <v>30.126927</v>
+        <v>30.0974593</v>
       </c>
       <c r="T36" t="n">
-        <v>74.161942</v>
+        <v>74.206666</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="V36" t="n">
-        <v>21311</v>
+        <v>71196</v>
       </c>
     </row>
     <row r="37">
@@ -3783,31 +3783,31 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>KULAR GRAIN MARKET</t>
+          <t>MALOOKPURA GRAIN MARKET</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>29.98347</v>
+        <v>30.132598</v>
       </c>
       <c r="I37" t="n">
-        <v>74.283652</v>
+        <v>74.343463</v>
       </c>
       <c r="J37" t="n">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="K37" t="n">
-        <v>30.090357</v>
+        <v>30.126927</v>
       </c>
       <c r="L37" t="n">
-        <v>74.20853700000001</v>
+        <v>74.161942</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -3815,7 +3815,7 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -3834,14 +3834,14 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S37" t="n">
-        <v>30.08793156</v>
+        <v>30.126927</v>
       </c>
       <c r="T37" t="n">
-        <v>74.20908439</v>
+        <v>74.161942</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="V37" t="n">
-        <v>30310</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="38">
@@ -3875,31 +3875,31 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>KULAR GRAIN MARKET</t>
+          <t>MAUJGARH GRAIN MARKET</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>29.98347</v>
+        <v>30.065633</v>
       </c>
       <c r="I38" t="n">
-        <v>74.283652</v>
+        <v>73.98462499999999</v>
       </c>
       <c r="J38" t="n">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="K38" t="n">
-        <v>30.090357</v>
+        <v>30.126927</v>
       </c>
       <c r="L38" t="n">
-        <v>74.20853700000001</v>
+        <v>74.161942</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -3926,14 +3926,14 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S38" t="n">
-        <v>30.08675444</v>
+        <v>30.126927</v>
       </c>
       <c r="T38" t="n">
-        <v>74.20888524</v>
+        <v>74.161942</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         </is>
       </c>
       <c r="V38" t="n">
-        <v>3784</v>
+        <v>34208</v>
       </c>
     </row>
     <row r="39">
@@ -3967,31 +3967,31 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>KUNDAL GRAIN MARKET</t>
+          <t>NIHAL KHERA GRAIN MARKET</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>30.216512</v>
+        <v>30.224829</v>
       </c>
       <c r="I39" t="n">
-        <v>74.269492</v>
+        <v>74.12361199999999</v>
       </c>
       <c r="J39" t="n">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="K39" t="n">
-        <v>30.175344</v>
+        <v>30.180346</v>
       </c>
       <c r="L39" t="n">
-        <v>74.178363</v>
+        <v>74.17439299999999</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -4018,14 +4018,14 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S39" t="n">
-        <v>30.17081207</v>
+        <v>30.15809938</v>
       </c>
       <c r="T39" t="n">
-        <v>74.18179719</v>
+        <v>74.16401603</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         </is>
       </c>
       <c r="V39" t="n">
-        <v>32401</v>
+        <v>54819.5</v>
       </c>
     </row>
     <row r="40">
@@ -4059,22 +4059,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>MALOOKPURA GRAIN MARKET</t>
+          <t>PANJKOSI GRAIN MARKET</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>30.132598</v>
+        <v>30.178444</v>
       </c>
       <c r="I40" t="n">
-        <v>74.343463</v>
+        <v>74.065141</v>
       </c>
       <c r="J40" t="n">
         <v>287</v>
@@ -4110,7 +4110,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S40" t="n">
@@ -4125,7 +4125,7 @@
         </is>
       </c>
       <c r="V40" t="n">
-        <v>73685</v>
+        <v>37768</v>
       </c>
     </row>
     <row r="41">
@@ -4151,22 +4151,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>MAUJGARH GRAIN MARKET</t>
+          <t>PATRE WALA GRAIN MARKET</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>30.065633</v>
+        <v>30.196706</v>
       </c>
       <c r="I41" t="n">
-        <v>73.98462499999999</v>
+        <v>74.04839699999999</v>
       </c>
       <c r="J41" t="n">
         <v>287</v>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S41" t="n">
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="V41" t="n">
-        <v>34208</v>
+        <v>29874.5</v>
       </c>
     </row>
     <row r="42">
@@ -4243,31 +4243,31 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>NARAINPURA GRAIN MARKET</t>
+          <t>RUKANPURA KHUI KHERA GRAIN MARKET</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>29.956267</v>
+        <v>30.035803</v>
       </c>
       <c r="I42" t="n">
-        <v>74.332578</v>
+        <v>74.111367</v>
       </c>
       <c r="J42" t="n">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="K42" t="n">
-        <v>30.090357</v>
+        <v>30.126927</v>
       </c>
       <c r="L42" t="n">
-        <v>74.20853700000001</v>
+        <v>74.161942</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -4294,14 +4294,14 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S42" t="n">
-        <v>30.08793156</v>
+        <v>30.126927</v>
       </c>
       <c r="T42" t="n">
-        <v>74.20908439</v>
+        <v>74.161942</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         </is>
       </c>
       <c r="V42" t="n">
-        <v>17701</v>
+        <v>56983.5</v>
       </c>
     </row>
     <row r="43">
@@ -4335,31 +4335,31 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>NIHAL KHERA GRAIN MARKET</t>
+          <t>SAIDANWALA GRAIN MARKET</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>30.224829</v>
+        <v>30.131281</v>
       </c>
       <c r="I43" t="n">
-        <v>74.12361199999999</v>
+        <v>74.103374</v>
       </c>
       <c r="J43" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K43" t="n">
-        <v>30.180346</v>
+        <v>30.126927</v>
       </c>
       <c r="L43" t="n">
-        <v>74.17439299999999</v>
+        <v>74.161942</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -4386,14 +4386,14 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S43" t="n">
-        <v>30.15809938</v>
+        <v>30.126927</v>
       </c>
       <c r="T43" t="n">
-        <v>74.16401603</v>
+        <v>74.161942</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="V43" t="n">
-        <v>54819.5</v>
+        <v>23195.5</v>
       </c>
     </row>
     <row r="44">
@@ -4427,22 +4427,22 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>PANJKOSI GRAIN MARKET</t>
+          <t>WAREYAM KHERA GRAIN MARKET</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>30.178444</v>
+        <v>30.029455</v>
       </c>
       <c r="I44" t="n">
-        <v>74.065141</v>
+        <v>74.077962</v>
       </c>
       <c r="J44" t="n">
         <v>287</v>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S44" t="n">
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="V44" t="n">
-        <v>37768</v>
+        <v>57368</v>
       </c>
     </row>
     <row r="45">
@@ -4519,31 +4519,31 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>PATRE WALA GRAIN MARKET</t>
+          <t>Bhadoo Waxing Plant</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>30.196706</v>
+        <v>29.983545</v>
       </c>
       <c r="I45" t="n">
-        <v>74.04839699999999</v>
+        <v>74.173574</v>
       </c>
       <c r="J45" t="n">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="K45" t="n">
-        <v>30.126927</v>
+        <v>30.105887</v>
       </c>
       <c r="L45" t="n">
-        <v>74.161942</v>
+        <v>74.18092900000001</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -4570,14 +4570,14 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S45" t="n">
-        <v>30.126927</v>
+        <v>30.10552983</v>
       </c>
       <c r="T45" t="n">
-        <v>74.161942</v>
+        <v>74.18014506</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         </is>
       </c>
       <c r="V45" t="n">
-        <v>29874.5</v>
+        <v>2487</v>
       </c>
     </row>
     <row r="46">
@@ -4611,31 +4611,31 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>RUKANPURA KHUI KHERA GRAIN MARKET</t>
+          <t>P.S. Waxing Plant</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>30.035803</v>
+        <v>30.254422</v>
       </c>
       <c r="I46" t="n">
-        <v>74.111367</v>
+        <v>74.126414</v>
       </c>
       <c r="J46" t="n">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="K46" t="n">
-        <v>30.126927</v>
+        <v>30.180346</v>
       </c>
       <c r="L46" t="n">
-        <v>74.161942</v>
+        <v>74.17439299999999</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -4662,14 +4662,14 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S46" t="n">
-        <v>30.126927</v>
+        <v>30.15809938</v>
       </c>
       <c r="T46" t="n">
-        <v>74.161942</v>
+        <v>74.16401603</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="V46" t="n">
-        <v>56983.5</v>
+        <v>29195</v>
       </c>
     </row>
     <row r="47">
@@ -4703,31 +4703,31 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SAIDANWALA GRAIN MARKET</t>
+          <t>Sandhu waxing plant</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>30.131281</v>
+        <v>30.247905</v>
       </c>
       <c r="I47" t="n">
-        <v>74.103374</v>
+        <v>74.129536</v>
       </c>
       <c r="J47" t="n">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="K47" t="n">
-        <v>30.126927</v>
+        <v>30.180346</v>
       </c>
       <c r="L47" t="n">
-        <v>74.161942</v>
+        <v>74.17439299999999</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -4735,7 +4735,7 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -4754,14 +4754,14 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S47" t="n">
-        <v>30.126927</v>
+        <v>30.15809938</v>
       </c>
       <c r="T47" t="n">
-        <v>74.161942</v>
+        <v>74.16401603</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="V47" t="n">
-        <v>23195.5</v>
+        <v>26795</v>
       </c>
     </row>
     <row r="48">
@@ -4795,31 +4795,31 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SITO GUNO GRAIN MARKET</t>
+          <t>Sri Ram cotton &amp; oil mill</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>30.027734</v>
+        <v>30.25374</v>
       </c>
       <c r="I48" t="n">
-        <v>74.36728100000001</v>
+        <v>74.122122</v>
       </c>
       <c r="J48" t="n">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="K48" t="n">
-        <v>30.090357</v>
+        <v>30.180346</v>
       </c>
       <c r="L48" t="n">
-        <v>74.20853700000001</v>
+        <v>74.17439299999999</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -4846,14 +4846,14 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S48" t="n">
-        <v>30.08793156</v>
+        <v>30.15809938</v>
       </c>
       <c r="T48" t="n">
-        <v>74.20908439</v>
+        <v>74.16401603</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         </is>
       </c>
       <c r="V48" t="n">
-        <v>71340</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="49">
@@ -4887,31 +4887,31 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>536</v>
+        <v>545</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SITO GUNO GRAIN MARKET</t>
+          <t>Near Mandir</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>30.027734</v>
+        <v>29.975306</v>
       </c>
       <c r="I49" t="n">
-        <v>74.36728100000001</v>
+        <v>74.164011</v>
       </c>
       <c r="J49" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="K49" t="n">
-        <v>30.090357</v>
+        <v>30.105887</v>
       </c>
       <c r="L49" t="n">
-        <v>74.20853700000001</v>
+        <v>74.18092900000001</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -4938,14 +4938,14 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S49" t="n">
-        <v>30.0974593</v>
+        <v>30.10552983</v>
       </c>
       <c r="T49" t="n">
-        <v>74.206666</v>
+        <v>74.18014506</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         </is>
       </c>
       <c r="V49" t="n">
-        <v>36210</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="50">
@@ -4979,31 +4979,31 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>537</v>
+        <v>546</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>VAJIDPUR BHOMA GRAIN MARKET</t>
+          <t>Near Gurdwara Sahib</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>29.951208</v>
+        <v>30.144184</v>
       </c>
       <c r="I50" t="n">
-        <v>74.380385</v>
+        <v>74.122771</v>
       </c>
       <c r="J50" t="n">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="K50" t="n">
-        <v>30.090357</v>
+        <v>30.126927</v>
       </c>
       <c r="L50" t="n">
-        <v>74.20853700000001</v>
+        <v>74.161942</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -5030,14 +5030,14 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S50" t="n">
-        <v>30.08793156</v>
+        <v>30.126927</v>
       </c>
       <c r="T50" t="n">
-        <v>74.20908439</v>
+        <v>74.161942</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         </is>
       </c>
       <c r="V50" t="n">
-        <v>43549</v>
+        <v>12630.5</v>
       </c>
     </row>
     <row r="51">
@@ -5071,22 +5071,22 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>WAREYAM KHERA GRAIN MARKET</t>
+          <t>Dera Jhangi wala</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>30.029455</v>
+        <v>30.161715</v>
       </c>
       <c r="I51" t="n">
-        <v>74.077962</v>
+        <v>73.987483</v>
       </c>
       <c r="J51" t="n">
         <v>287</v>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S51" t="n">
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="V51" t="n">
-        <v>57368</v>
+        <v>13803</v>
       </c>
     </row>
     <row r="52">
@@ -5163,22 +5163,22 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bhadoo Waxing Plant</t>
+          <t>Near Jandwala Meera Sangla purchase center</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>29.983545</v>
+        <v>30.21135</v>
       </c>
       <c r="I52" t="n">
-        <v>74.173574</v>
+        <v>74.02397999999999</v>
       </c>
       <c r="J52" t="n">
         <v>287</v>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S52" t="n">
@@ -5229,7 +5229,7 @@
         </is>
       </c>
       <c r="V52" t="n">
-        <v>2487</v>
+        <v>9145</v>
       </c>
     </row>
     <row r="53">
@@ -5255,31 +5255,31 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>P.S. Waxing Plant</t>
+          <t>GHARHIANA GRAIN MARKET</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>30.254422</v>
+        <v>30.296726</v>
       </c>
       <c r="I53" t="n">
-        <v>74.126414</v>
+        <v>74.263169</v>
       </c>
       <c r="J53" t="n">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="K53" t="n">
-        <v>30.180346</v>
+        <v>30.175344</v>
       </c>
       <c r="L53" t="n">
-        <v>74.17439299999999</v>
+        <v>74.178363</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -5306,14 +5306,14 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S53" t="n">
-        <v>30.15809938</v>
+        <v>30.17081207</v>
       </c>
       <c r="T53" t="n">
-        <v>74.16401603</v>
+        <v>74.18179719</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         </is>
       </c>
       <c r="V53" t="n">
-        <v>29195</v>
+        <v>17622.5</v>
       </c>
     </row>
     <row r="54">
@@ -5347,22 +5347,22 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sandhu waxing plant</t>
+          <t>MAMMU KHERA GRAIN MARKET</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>30.247905</v>
+        <v>30.285139</v>
       </c>
       <c r="I54" t="n">
-        <v>74.129536</v>
+        <v>74.172681</v>
       </c>
       <c r="J54" t="n">
         <v>285</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S54" t="n">
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="V54" t="n">
-        <v>26795</v>
+        <v>2347.5</v>
       </c>
     </row>
     <row r="55">
@@ -5439,22 +5439,22 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sri Ram cotton &amp; oil mill</t>
+          <t>MAMMU KHERA GRAIN MARKET</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>30.25374</v>
+        <v>30.285139</v>
       </c>
       <c r="I55" t="n">
-        <v>74.122122</v>
+        <v>74.172681</v>
       </c>
       <c r="J55" t="n">
         <v>285</v>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -5490,14 +5490,14 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S55" t="n">
-        <v>30.15809938</v>
+        <v>30.17767461</v>
       </c>
       <c r="T55" t="n">
-        <v>74.16401603</v>
+        <v>74.17723581</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         </is>
       </c>
       <c r="V55" t="n">
-        <v>7950</v>
+        <v>40337.5</v>
       </c>
     </row>
     <row r="56">
@@ -5531,31 +5531,31 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Near Mandir</t>
+          <t>MURADWALA GRAIN MARKET</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>29.975306</v>
+        <v>30.260814</v>
       </c>
       <c r="I56" t="n">
-        <v>74.164011</v>
+        <v>74.269329</v>
       </c>
       <c r="J56" t="n">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="K56" t="n">
-        <v>30.126927</v>
+        <v>30.175344</v>
       </c>
       <c r="L56" t="n">
-        <v>74.161942</v>
+        <v>74.178363</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -5582,14 +5582,14 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S56" t="n">
-        <v>30.126927</v>
+        <v>30.17081207</v>
       </c>
       <c r="T56" t="n">
-        <v>74.161942</v>
+        <v>74.18179719</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
@@ -5597,7 +5597,7 @@
         </is>
       </c>
       <c r="V56" t="n">
-        <v>5500</v>
+        <v>56502.5</v>
       </c>
     </row>
     <row r="57">
@@ -5623,31 +5623,31 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Near Gurdwara Sahib</t>
+          <t>KUHADIANWALI GRAIN MARKET</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>30.144184</v>
+        <v>30.290503</v>
       </c>
       <c r="I57" t="n">
-        <v>74.122771</v>
+        <v>74.220803</v>
       </c>
       <c r="J57" t="n">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="K57" t="n">
-        <v>30.126927</v>
+        <v>30.175344</v>
       </c>
       <c r="L57" t="n">
-        <v>74.161942</v>
+        <v>74.178363</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -5674,14 +5674,14 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S57" t="n">
-        <v>30.126927</v>
+        <v>30.17081207</v>
       </c>
       <c r="T57" t="n">
-        <v>74.161942</v>
+        <v>74.18179719</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         </is>
       </c>
       <c r="V57" t="n">
-        <v>12630.5</v>
+        <v>43110</v>
       </c>
     </row>
     <row r="58">
@@ -5715,31 +5715,31 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>547</v>
+        <v>560</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dera Jhangi wala</t>
+          <t>KHIUWALA DHAB GRAIN MARKET</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>30.161715</v>
+        <v>30.251211</v>
       </c>
       <c r="I58" t="n">
-        <v>73.987483</v>
+        <v>74.011872</v>
       </c>
       <c r="J58" t="n">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="K58" t="n">
-        <v>30.126927</v>
+        <v>30.180346</v>
       </c>
       <c r="L58" t="n">
-        <v>74.161942</v>
+        <v>74.17439299999999</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -5766,14 +5766,14 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S58" t="n">
-        <v>30.126927</v>
+        <v>30.15809938</v>
       </c>
       <c r="T58" t="n">
-        <v>74.161942</v>
+        <v>74.16401603</v>
       </c>
       <c r="U58" t="inlineStr">
         <is>
@@ -5781,7 +5781,7 @@
         </is>
       </c>
       <c r="V58" t="n">
-        <v>13803</v>
+        <v>128218</v>
       </c>
     </row>
     <row r="59">
@@ -5807,22 +5807,22 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>548</v>
+        <v>565</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Near Jandwala Meera Sangla purchase center</t>
+          <t>RAMKOT GRAIN MARKET</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>30.21135</v>
+        <v>30.280985</v>
       </c>
       <c r="I59" t="n">
-        <v>74.02397999999999</v>
+        <v>74.057811</v>
       </c>
       <c r="J59" t="n">
         <v>285</v>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S59" t="n">
@@ -5873,7 +5873,7 @@
         </is>
       </c>
       <c r="V59" t="n">
-        <v>9145</v>
+        <v>62709.5</v>
       </c>
     </row>
     <row r="60">
@@ -5899,22 +5899,22 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>549</v>
+        <v>612</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>GHARHIANA GRAIN MARKET</t>
+          <t>KANDHWALA HAZARKHAN GRAIN MARKET</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>30.296726</v>
+        <v>30.3064</v>
       </c>
       <c r="I60" t="n">
-        <v>74.263169</v>
+        <v>74.22073899999999</v>
       </c>
       <c r="J60" t="n">
         <v>279</v>
@@ -5950,7 +5950,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S60" t="n">
@@ -5965,7 +5965,7 @@
         </is>
       </c>
       <c r="V60" t="n">
-        <v>17622.5</v>
+        <v>47189.5</v>
       </c>
     </row>
     <row r="61">
@@ -5986,36 +5986,36 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>JALANDHAR</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>550</v>
+        <v>1046</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>MAMMU KHERA GRAIN MARKET</t>
+          <t xml:space="preserve">ADAMPUR  </t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>30.285139</v>
+        <v>31.425406</v>
       </c>
       <c r="I61" t="n">
-        <v>74.172681</v>
+        <v>75.719528</v>
       </c>
       <c r="J61" t="n">
-        <v>285</v>
+        <v>522</v>
       </c>
       <c r="K61" t="n">
-        <v>30.180346</v>
+        <v>31.4204409</v>
       </c>
       <c r="L61" t="n">
-        <v>74.17439299999999</v>
+        <v>75.69994199999999</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>402</v>
+        <v>625</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -6037,19 +6037,19 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>JALANDHAR</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S61" t="n">
-        <v>30.17767461</v>
+        <v>31.408658</v>
       </c>
       <c r="T61" t="n">
-        <v>74.17723581</v>
+        <v>75.685958</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         </is>
       </c>
       <c r="V61" t="n">
-        <v>42685</v>
+        <v>21500</v>
       </c>
     </row>
     <row r="62">
@@ -6078,36 +6078,36 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>SRI MUKTSAR SAHIB</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>551</v>
+        <v>1577</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>MURADWALA GRAIN MARKET</t>
+          <t>BHAGSAR GRAIN MARKET</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>30.260814</v>
+        <v>30.4426709</v>
       </c>
       <c r="I62" t="n">
-        <v>74.269329</v>
+        <v>74.4101264</v>
       </c>
       <c r="J62" t="n">
-        <v>279</v>
+        <v>1455</v>
       </c>
       <c r="K62" t="n">
-        <v>30.175344</v>
+        <v>30.450458</v>
       </c>
       <c r="L62" t="n">
-        <v>74.178363</v>
+        <v>74.489422</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>401</v>
+        <v>866</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -6129,19 +6129,19 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>MALERKOTLA</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S62" t="n">
-        <v>30.17081207</v>
+        <v>30.458388</v>
       </c>
       <c r="T62" t="n">
-        <v>74.18179719</v>
+        <v>74.453514</v>
       </c>
       <c r="U62" t="inlineStr">
         <is>
@@ -6149,7 +6149,7 @@
         </is>
       </c>
       <c r="V62" t="n">
-        <v>56502.5</v>
+        <v>88594</v>
       </c>
     </row>
     <row r="63">
@@ -6170,36 +6170,36 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>SRI MUKTSAR SAHIB</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>552</v>
+        <v>1577</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>KUHADIANWALI GRAIN MARKET</t>
+          <t>BHAGSAR GRAIN MARKET</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>30.290503</v>
+        <v>30.4426709</v>
       </c>
       <c r="I63" t="n">
-        <v>74.220803</v>
+        <v>74.4101264</v>
       </c>
       <c r="J63" t="n">
-        <v>279</v>
+        <v>1455</v>
       </c>
       <c r="K63" t="n">
-        <v>30.175344</v>
+        <v>30.450458</v>
       </c>
       <c r="L63" t="n">
-        <v>74.178363</v>
+        <v>74.489422</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -6207,7 +6207,7 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>401</v>
+        <v>870</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -6221,19 +6221,19 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>MALERKOTLA</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>Abohar</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S63" t="n">
-        <v>30.17081207</v>
+        <v>30.458388</v>
       </c>
       <c r="T63" t="n">
-        <v>74.18179719</v>
+        <v>74.453514</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
         </is>
       </c>
       <c r="V63" t="n">
-        <v>43110</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="64">
@@ -6262,63 +6262,63 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t>SRI MUKTSAR SAHIB</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Stor</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>1577</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>BHAGSAR GRAIN MARKET</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>30.4426709</v>
+      </c>
+      <c r="I64" t="n">
+        <v>74.4101264</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1455</v>
+      </c>
+      <c r="K64" t="n">
+        <v>30.450458</v>
+      </c>
+      <c r="L64" t="n">
+        <v>74.489422</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Depot</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>875</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>agah</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Haryana</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
           <t>MALERKOTLA</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>AHMEDGARH</t>
-        </is>
-      </c>
-      <c r="F64" t="n">
-        <v>1322</v>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>AHMEDGARH</t>
-        </is>
-      </c>
-      <c r="H64" t="n">
-        <v>30.67924</v>
-      </c>
-      <c r="I64" t="n">
-        <v>75.84139999999999</v>
-      </c>
-      <c r="J64" t="n">
-        <v>703</v>
-      </c>
-      <c r="K64" t="n">
-        <v>30.618135</v>
-      </c>
-      <c r="L64" t="n">
-        <v>75.435686</v>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>Depot</t>
-        </is>
-      </c>
-      <c r="N64" t="n">
-        <v>864</v>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>agah</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>Haryana</t>
-        </is>
-      </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>MALERKOTLA</t>
-        </is>
-      </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>AHMEDGARH</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S64" t="n">
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="V64" t="n">
-        <v>197630</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="65">
@@ -6354,63 +6354,63 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
+          <t>SRI MUKTSAR SAHIB</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Stor</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>1577</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>BHAGSAR GRAIN MARKET</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>30.4426709</v>
+      </c>
+      <c r="I65" t="n">
+        <v>74.4101264</v>
+      </c>
+      <c r="J65" t="n">
+        <v>1455</v>
+      </c>
+      <c r="K65" t="n">
+        <v>30.450458</v>
+      </c>
+      <c r="L65" t="n">
+        <v>74.489422</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Depot</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>876</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>agah</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Haryana</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
           <t>MALERKOTLA</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>AHMEDGARH</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>1322</v>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>AHMEDGARH</t>
-        </is>
-      </c>
-      <c r="H65" t="n">
-        <v>30.67924</v>
-      </c>
-      <c r="I65" t="n">
-        <v>75.84139999999999</v>
-      </c>
-      <c r="J65" t="n">
-        <v>703</v>
-      </c>
-      <c r="K65" t="n">
-        <v>30.618135</v>
-      </c>
-      <c r="L65" t="n">
-        <v>75.435686</v>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>Depot</t>
-        </is>
-      </c>
-      <c r="N65" t="n">
-        <v>865</v>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>agah</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>Haryana</t>
-        </is>
-      </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>MALERKOTLA</t>
-        </is>
-      </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>AHMEDGARH</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S65" t="n">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="V65" t="n">
-        <v>16680</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="66">
@@ -6446,36 +6446,36 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>MALERKOTLA</t>
+          <t>SRI MUKTSAR SAHIB</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AHMEDGARH</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1322</v>
+        <v>1597</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>AHMEDGARH</t>
+          <t>MAHABADAR GRAIN MARKET</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>30.67924</v>
+        <v>30.419565</v>
       </c>
       <c r="I66" t="n">
-        <v>75.84139999999999</v>
+        <v>74.44302166999999</v>
       </c>
       <c r="J66" t="n">
-        <v>703</v>
+        <v>1455</v>
       </c>
       <c r="K66" t="n">
-        <v>30.618135</v>
+        <v>30.450458</v>
       </c>
       <c r="L66" t="n">
-        <v>75.435686</v>
+        <v>74.489422</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>AHMEDGARH</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S66" t="n">
@@ -6517,7 +6517,7 @@
         </is>
       </c>
       <c r="V66" t="n">
-        <v>42630</v>
+        <v>38086</v>
       </c>
     </row>
     <row r="67">
@@ -6538,63 +6538,63 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t>SRI MUKTSAR SAHIB</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Stor</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>1597</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>MAHABADAR GRAIN MARKET</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>30.419565</v>
+      </c>
+      <c r="I67" t="n">
+        <v>74.44302166999999</v>
+      </c>
+      <c r="J67" t="n">
+        <v>1455</v>
+      </c>
+      <c r="K67" t="n">
+        <v>30.450458</v>
+      </c>
+      <c r="L67" t="n">
+        <v>74.489422</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Depot</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>872</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>agah</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Haryana</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
           <t>MALERKOTLA</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>AHMEDGARH</t>
-        </is>
-      </c>
-      <c r="F67" t="n">
-        <v>1322</v>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>AHMEDGARH</t>
-        </is>
-      </c>
-      <c r="H67" t="n">
-        <v>30.67924</v>
-      </c>
-      <c r="I67" t="n">
-        <v>75.84139999999999</v>
-      </c>
-      <c r="J67" t="n">
-        <v>703</v>
-      </c>
-      <c r="K67" t="n">
-        <v>30.618135</v>
-      </c>
-      <c r="L67" t="n">
-        <v>75.435686</v>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>Depot</t>
-        </is>
-      </c>
-      <c r="N67" t="n">
-        <v>868</v>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>agah</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>Haryana</t>
-        </is>
-      </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>MALERKOTLA</t>
-        </is>
-      </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>AHMEDGARH</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S67" t="n">
@@ -6609,7 +6609,7 @@
         </is>
       </c>
       <c r="V67" t="n">
-        <v>10000</v>
+        <v>30720</v>
       </c>
     </row>
     <row r="68">
@@ -6630,63 +6630,63 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t>SRI MUKTSAR SAHIB</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Stor</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>1597</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>MAHABADAR GRAIN MARKET</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>30.419565</v>
+      </c>
+      <c r="I68" t="n">
+        <v>74.44302166999999</v>
+      </c>
+      <c r="J68" t="n">
+        <v>1455</v>
+      </c>
+      <c r="K68" t="n">
+        <v>30.450458</v>
+      </c>
+      <c r="L68" t="n">
+        <v>74.489422</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Depot</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>877</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>agah</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Haryana</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
           <t>MALERKOTLA</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>AHMEDGARH</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
-        <v>1322</v>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>AHMEDGARH</t>
-        </is>
-      </c>
-      <c r="H68" t="n">
-        <v>30.67924</v>
-      </c>
-      <c r="I68" t="n">
-        <v>75.84139999999999</v>
-      </c>
-      <c r="J68" t="n">
-        <v>703</v>
-      </c>
-      <c r="K68" t="n">
-        <v>30.618135</v>
-      </c>
-      <c r="L68" t="n">
-        <v>75.435686</v>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>Depot</t>
-        </is>
-      </c>
-      <c r="N68" t="n">
-        <v>869</v>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>agah</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>Haryana</t>
-        </is>
-      </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>MALERKOTLA</t>
-        </is>
-      </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>AHMEDGARH</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S68" t="n">
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="V68" t="n">
-        <v>10000</v>
+        <v>5127</v>
       </c>
     </row>
     <row r="69">
@@ -6722,63 +6722,63 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
+          <t>SRI MUKTSAR SAHIB</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Stor</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>1607</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>sri muktsar sahib grain market</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>30.4726737</v>
+      </c>
+      <c r="I69" t="n">
+        <v>74.5049465</v>
+      </c>
+      <c r="J69" t="n">
+        <v>1512</v>
+      </c>
+      <c r="K69" t="n">
+        <v>30.4713293</v>
+      </c>
+      <c r="L69" t="n">
+        <v>74.5033904</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Depot</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>864</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>agah</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Haryana</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
           <t>MALERKOTLA</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>AHMEDGARH</t>
-        </is>
-      </c>
-      <c r="F69" t="n">
-        <v>1322</v>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>AHMEDGARH</t>
-        </is>
-      </c>
-      <c r="H69" t="n">
-        <v>30.67924</v>
-      </c>
-      <c r="I69" t="n">
-        <v>75.84139999999999</v>
-      </c>
-      <c r="J69" t="n">
-        <v>703</v>
-      </c>
-      <c r="K69" t="n">
-        <v>30.618135</v>
-      </c>
-      <c r="L69" t="n">
-        <v>75.435686</v>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>Depot</t>
-        </is>
-      </c>
-      <c r="N69" t="n">
-        <v>870</v>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>agah</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>Haryana</t>
-        </is>
-      </c>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>MALERKOTLA</t>
-        </is>
-      </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>AHMEDGARH</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S69" t="n">
@@ -6793,7 +6793,7 @@
         </is>
       </c>
       <c r="V69" t="n">
-        <v>10000</v>
+        <v>294680</v>
       </c>
     </row>
     <row r="70">
@@ -6814,63 +6814,63 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t>SRI MUKTSAR SAHIB</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Stor</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>1607</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>sri muktsar sahib grain market</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>30.4726737</v>
+      </c>
+      <c r="I70" t="n">
+        <v>74.5049465</v>
+      </c>
+      <c r="J70" t="n">
+        <v>1512</v>
+      </c>
+      <c r="K70" t="n">
+        <v>30.4713293</v>
+      </c>
+      <c r="L70" t="n">
+        <v>74.5033904</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Depot</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>865</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>agah</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Haryana</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
           <t>MALERKOTLA</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>AHMEDGARH</t>
-        </is>
-      </c>
-      <c r="F70" t="n">
-        <v>1322</v>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>AHMEDGARH</t>
-        </is>
-      </c>
-      <c r="H70" t="n">
-        <v>30.67924</v>
-      </c>
-      <c r="I70" t="n">
-        <v>75.84139999999999</v>
-      </c>
-      <c r="J70" t="n">
-        <v>703</v>
-      </c>
-      <c r="K70" t="n">
-        <v>30.618135</v>
-      </c>
-      <c r="L70" t="n">
-        <v>75.435686</v>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>Depot</t>
-        </is>
-      </c>
-      <c r="N70" t="n">
-        <v>871</v>
-      </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>agah</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>Haryana</t>
-        </is>
-      </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>MALERKOTLA</t>
-        </is>
-      </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>AHMEDGARH</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S70" t="n">
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="V70" t="n">
-        <v>30720</v>
+        <v>16680</v>
       </c>
     </row>
     <row r="71">
@@ -6906,63 +6906,63 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
+          <t>SRI MUKTSAR SAHIB</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Stor</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>1607</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>sri muktsar sahib grain market</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>30.4726737</v>
+      </c>
+      <c r="I71" t="n">
+        <v>74.5049465</v>
+      </c>
+      <c r="J71" t="n">
+        <v>1512</v>
+      </c>
+      <c r="K71" t="n">
+        <v>30.4713293</v>
+      </c>
+      <c r="L71" t="n">
+        <v>74.5033904</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Depot</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>867</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>agah</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Haryana</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
           <t>MALERKOTLA</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>AHMEDGARH</t>
-        </is>
-      </c>
-      <c r="F71" t="n">
-        <v>1322</v>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>AHMEDGARH</t>
-        </is>
-      </c>
-      <c r="H71" t="n">
-        <v>30.67924</v>
-      </c>
-      <c r="I71" t="n">
-        <v>75.84139999999999</v>
-      </c>
-      <c r="J71" t="n">
-        <v>703</v>
-      </c>
-      <c r="K71" t="n">
-        <v>30.618135</v>
-      </c>
-      <c r="L71" t="n">
-        <v>75.435686</v>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>Depot</t>
-        </is>
-      </c>
-      <c r="N71" t="n">
-        <v>872</v>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>agah</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>Haryana</t>
-        </is>
-      </c>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>MALERKOTLA</t>
-        </is>
-      </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>AHMEDGARH</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S71" t="n">
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="V71" t="n">
-        <v>1080</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="72">
@@ -6998,63 +6998,63 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
+          <t>SRI MUKTSAR SAHIB</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Stor</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>1607</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>sri muktsar sahib grain market</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>30.4726737</v>
+      </c>
+      <c r="I72" t="n">
+        <v>74.5049465</v>
+      </c>
+      <c r="J72" t="n">
+        <v>1512</v>
+      </c>
+      <c r="K72" t="n">
+        <v>30.4713293</v>
+      </c>
+      <c r="L72" t="n">
+        <v>74.5033904</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Depot</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>868</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>agah</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Haryana</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
           <t>MALERKOTLA</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>AHMEDGARH</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
-        <v>1322</v>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>AHMEDGARH</t>
-        </is>
-      </c>
-      <c r="H72" t="n">
-        <v>30.67924</v>
-      </c>
-      <c r="I72" t="n">
-        <v>75.84139999999999</v>
-      </c>
-      <c r="J72" t="n">
-        <v>703</v>
-      </c>
-      <c r="K72" t="n">
-        <v>30.618135</v>
-      </c>
-      <c r="L72" t="n">
-        <v>75.435686</v>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>Depot</t>
-        </is>
-      </c>
-      <c r="N72" t="n">
-        <v>873</v>
-      </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>agah</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>Haryana</t>
-        </is>
-      </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>MALERKOTLA</t>
-        </is>
-      </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>AHMEDGARH</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S72" t="n">
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="V72" t="n">
-        <v>29640</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="73">
@@ -7090,63 +7090,63 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
+          <t>SRI MUKTSAR SAHIB</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Stor</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>1607</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>sri muktsar sahib grain market</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>30.4726737</v>
+      </c>
+      <c r="I73" t="n">
+        <v>74.5049465</v>
+      </c>
+      <c r="J73" t="n">
+        <v>1512</v>
+      </c>
+      <c r="K73" t="n">
+        <v>30.4713293</v>
+      </c>
+      <c r="L73" t="n">
+        <v>74.5033904</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Depot</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>869</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>agah</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Haryana</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
           <t>MALERKOTLA</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AHMEDGARH</t>
-        </is>
-      </c>
-      <c r="F73" t="n">
-        <v>1322</v>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>AHMEDGARH</t>
-        </is>
-      </c>
-      <c r="H73" t="n">
-        <v>30.67924</v>
-      </c>
-      <c r="I73" t="n">
-        <v>75.84139999999999</v>
-      </c>
-      <c r="J73" t="n">
-        <v>703</v>
-      </c>
-      <c r="K73" t="n">
-        <v>30.618135</v>
-      </c>
-      <c r="L73" t="n">
-        <v>75.435686</v>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>Depot</t>
-        </is>
-      </c>
-      <c r="N73" t="n">
-        <v>877</v>
-      </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>agah</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>Haryana</t>
-        </is>
-      </c>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>MALERKOTLA</t>
-        </is>
-      </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>AHMEDGARH</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S73" t="n">
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="V73" t="n">
-        <v>9950</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="74">
@@ -7182,63 +7182,63 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
+          <t>SRI MUKTSAR SAHIB</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Stor</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>1607</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>sri muktsar sahib grain market</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>30.4726737</v>
+      </c>
+      <c r="I74" t="n">
+        <v>74.5049465</v>
+      </c>
+      <c r="J74" t="n">
+        <v>1512</v>
+      </c>
+      <c r="K74" t="n">
+        <v>30.4713293</v>
+      </c>
+      <c r="L74" t="n">
+        <v>74.5033904</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Depot</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>871</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>agah</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Haryana</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
           <t>MALERKOTLA</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AHMEDGARH</t>
-        </is>
-      </c>
-      <c r="F74" t="n">
-        <v>1323</v>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>BHIKHAMPUR BEGOWAL</t>
-        </is>
-      </c>
-      <c r="H74" t="n">
-        <v>30.61296</v>
-      </c>
-      <c r="I74" t="n">
-        <v>75.84106</v>
-      </c>
-      <c r="J74" t="n">
-        <v>999</v>
-      </c>
-      <c r="K74" t="n">
-        <v>30.561546</v>
-      </c>
-      <c r="L74" t="n">
-        <v>75.352118</v>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>Depot</t>
-        </is>
-      </c>
-      <c r="N74" t="n">
-        <v>867</v>
-      </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>agah</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>Haryana</t>
-        </is>
-      </c>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>MALERKOTLA</t>
-        </is>
-      </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>AHMEDGARH</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S74" t="n">
@@ -7253,7 +7253,7 @@
         </is>
       </c>
       <c r="V74" t="n">
-        <v>10000</v>
+        <v>30720</v>
       </c>
     </row>
     <row r="75">
@@ -7274,63 +7274,63 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
+          <t>SRI MUKTSAR SAHIB</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Stor</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>1607</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>sri muktsar sahib grain market</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>30.4726737</v>
+      </c>
+      <c r="I75" t="n">
+        <v>74.5049465</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1512</v>
+      </c>
+      <c r="K75" t="n">
+        <v>30.4713293</v>
+      </c>
+      <c r="L75" t="n">
+        <v>74.5033904</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Depot</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>873</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>agah</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Haryana</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
           <t>MALERKOTLA</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AHMEDGARH</t>
-        </is>
-      </c>
-      <c r="F75" t="n">
-        <v>1323</v>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>BHIKHAMPUR BEGOWAL</t>
-        </is>
-      </c>
-      <c r="H75" t="n">
-        <v>30.61296</v>
-      </c>
-      <c r="I75" t="n">
-        <v>75.84106</v>
-      </c>
-      <c r="J75" t="n">
-        <v>999</v>
-      </c>
-      <c r="K75" t="n">
-        <v>30.561546</v>
-      </c>
-      <c r="L75" t="n">
-        <v>75.352118</v>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>Depot</t>
-        </is>
-      </c>
-      <c r="N75" t="n">
-        <v>875</v>
-      </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>agah</t>
-        </is>
-      </c>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>Haryana</t>
-        </is>
-      </c>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>MALERKOTLA</t>
-        </is>
-      </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>AHMEDGARH</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S75" t="n">
@@ -7345,7 +7345,7 @@
         </is>
       </c>
       <c r="V75" t="n">
-        <v>5000</v>
+        <v>29640</v>
       </c>
     </row>
     <row r="76">
@@ -7366,63 +7366,63 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
+          <t>SRI MUKTSAR SAHIB</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Stor</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>1607</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>sri muktsar sahib grain market</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>30.4726737</v>
+      </c>
+      <c r="I76" t="n">
+        <v>74.5049465</v>
+      </c>
+      <c r="J76" t="n">
+        <v>1512</v>
+      </c>
+      <c r="K76" t="n">
+        <v>30.4713293</v>
+      </c>
+      <c r="L76" t="n">
+        <v>74.5033904</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Depot</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>874</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>agah</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Haryana</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
           <t>MALERKOTLA</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AHMEDGARH</t>
-        </is>
-      </c>
-      <c r="F76" t="n">
-        <v>1323</v>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>BHIKHAMPUR BEGOWAL</t>
-        </is>
-      </c>
-      <c r="H76" t="n">
-        <v>30.61296</v>
-      </c>
-      <c r="I76" t="n">
-        <v>75.84106</v>
-      </c>
-      <c r="J76" t="n">
-        <v>999</v>
-      </c>
-      <c r="K76" t="n">
-        <v>30.561546</v>
-      </c>
-      <c r="L76" t="n">
-        <v>75.352118</v>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>Depot</t>
-        </is>
-      </c>
-      <c r="N76" t="n">
-        <v>876</v>
-      </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>agah</t>
-        </is>
-      </c>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>Haryana</t>
-        </is>
-      </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>MALERKOTLA</t>
-        </is>
-      </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>AHMEDGARH</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S76" t="n">
@@ -7437,7 +7437,7 @@
         </is>
       </c>
       <c r="V76" t="n">
-        <v>5000</v>
+        <v>28460</v>
       </c>
     </row>
     <row r="77">
@@ -7458,63 +7458,63 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
+          <t>SRI MUKTSAR SAHIB</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Stor</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>1607</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>sri muktsar sahib grain market</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>30.4726737</v>
+      </c>
+      <c r="I77" t="n">
+        <v>74.5049465</v>
+      </c>
+      <c r="J77" t="n">
+        <v>1512</v>
+      </c>
+      <c r="K77" t="n">
+        <v>30.4713293</v>
+      </c>
+      <c r="L77" t="n">
+        <v>74.5033904</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Depot</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>877</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>agah</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Haryana</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
           <t>MALERKOTLA</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AHMEDGARH</t>
-        </is>
-      </c>
-      <c r="F77" t="n">
-        <v>1323</v>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>BHIKHAMPUR BEGOWAL</t>
-        </is>
-      </c>
-      <c r="H77" t="n">
-        <v>30.61296</v>
-      </c>
-      <c r="I77" t="n">
-        <v>75.84106</v>
-      </c>
-      <c r="J77" t="n">
-        <v>999</v>
-      </c>
-      <c r="K77" t="n">
-        <v>30.561546</v>
-      </c>
-      <c r="L77" t="n">
-        <v>75.352118</v>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>Depot</t>
-        </is>
-      </c>
-      <c r="N77" t="n">
-        <v>878</v>
-      </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t>agah</t>
-        </is>
-      </c>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>Haryana</t>
-        </is>
-      </c>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>MALERKOTLA</t>
-        </is>
-      </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>AHMEDGARH</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S77" t="n">
@@ -7529,7 +7529,7 @@
         </is>
       </c>
       <c r="V77" t="n">
-        <v>20480</v>
+        <v>15353</v>
       </c>
     </row>
     <row r="78">
@@ -7550,63 +7550,63 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
+          <t>SRI MUKTSAR SAHIB</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Stor</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>1607</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>sri muktsar sahib grain market</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>30.4726737</v>
+      </c>
+      <c r="I78" t="n">
+        <v>74.5049465</v>
+      </c>
+      <c r="J78" t="n">
+        <v>1512</v>
+      </c>
+      <c r="K78" t="n">
+        <v>30.4713293</v>
+      </c>
+      <c r="L78" t="n">
+        <v>74.5033904</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Depot</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>878</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>agah</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Haryana</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
           <t>MALERKOTLA</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AHMEDGARH</t>
-        </is>
-      </c>
-      <c r="F78" t="n">
-        <v>1323</v>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>BHIKHAMPUR BEGOWAL</t>
-        </is>
-      </c>
-      <c r="H78" t="n">
-        <v>30.61296</v>
-      </c>
-      <c r="I78" t="n">
-        <v>75.84106</v>
-      </c>
-      <c r="J78" t="n">
-        <v>999</v>
-      </c>
-      <c r="K78" t="n">
-        <v>30.561546</v>
-      </c>
-      <c r="L78" t="n">
-        <v>75.352118</v>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>Depot</t>
-        </is>
-      </c>
-      <c r="N78" t="n">
-        <v>879</v>
-      </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>agah</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>Haryana</t>
-        </is>
-      </c>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>MALERKOTLA</t>
-        </is>
-      </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>AHMEDGARH</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S78" t="n">
@@ -7621,7 +7621,7 @@
         </is>
       </c>
       <c r="V78" t="n">
-        <v>18000</v>
+        <v>20480</v>
       </c>
     </row>
     <row r="79">
@@ -7642,63 +7642,63 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
+          <t>SRI MUKTSAR SAHIB</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Stor</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>1607</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>sri muktsar sahib grain market</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>30.4726737</v>
+      </c>
+      <c r="I79" t="n">
+        <v>74.5049465</v>
+      </c>
+      <c r="J79" t="n">
+        <v>1512</v>
+      </c>
+      <c r="K79" t="n">
+        <v>30.4713293</v>
+      </c>
+      <c r="L79" t="n">
+        <v>74.5033904</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Depot</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>879</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>agah</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Haryana</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
           <t>MALERKOTLA</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AHMEDGARH</t>
-        </is>
-      </c>
-      <c r="F79" t="n">
-        <v>1324</v>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>DHALER KHURD</t>
-        </is>
-      </c>
-      <c r="H79" t="n">
-        <v>30.59296</v>
-      </c>
-      <c r="I79" t="n">
-        <v>75.78903</v>
-      </c>
-      <c r="J79" t="n">
-        <v>216</v>
-      </c>
-      <c r="K79" t="n">
-        <v>30.5076194</v>
-      </c>
-      <c r="L79" t="n">
-        <v>74.958715</v>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>Depot</t>
-        </is>
-      </c>
-      <c r="N79" t="n">
-        <v>864</v>
-      </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>agah</t>
-        </is>
-      </c>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>Haryana</t>
-        </is>
-      </c>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>MALERKOTLA</t>
-        </is>
-      </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>AHMEDGARH</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S79" t="n">
@@ -7713,7 +7713,7 @@
         </is>
       </c>
       <c r="V79" t="n">
-        <v>41830</v>
+        <v>20480</v>
       </c>
     </row>
     <row r="80">
@@ -7734,63 +7734,63 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
+          <t>SRI MUKTSAR SAHIB</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Stor</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>1607</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>sri muktsar sahib grain market</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>30.4726737</v>
+      </c>
+      <c r="I80" t="n">
+        <v>74.5049465</v>
+      </c>
+      <c r="J80" t="n">
+        <v>1512</v>
+      </c>
+      <c r="K80" t="n">
+        <v>30.4713293</v>
+      </c>
+      <c r="L80" t="n">
+        <v>74.5033904</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Depot</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>880</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>agah</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Haryana</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
           <t>MALERKOTLA</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AHMEDGARH</t>
-        </is>
-      </c>
-      <c r="F80" t="n">
-        <v>1325</v>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>KANGANWAL</t>
-        </is>
-      </c>
-      <c r="H80" t="n">
-        <v>30.61907</v>
-      </c>
-      <c r="I80" t="n">
-        <v>75.8098</v>
-      </c>
-      <c r="J80" t="n">
-        <v>217</v>
-      </c>
-      <c r="K80" t="n">
-        <v>30.51445</v>
-      </c>
-      <c r="L80" t="n">
-        <v>74.89836</v>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>Depot</t>
-        </is>
-      </c>
-      <c r="N80" t="n">
-        <v>864</v>
-      </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>agah</t>
-        </is>
-      </c>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>Haryana</t>
-        </is>
-      </c>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>MALERKOTLA</t>
-        </is>
-      </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>AHMEDGARH</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S80" t="n">
@@ -7805,7 +7805,7 @@
         </is>
       </c>
       <c r="V80" t="n">
-        <v>55220</v>
+        <v>15360</v>
       </c>
     </row>
     <row r="81">
@@ -7826,36 +7826,36 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>MALERKOTLA</t>
+          <t>SRI MUKTSAR SAHIB</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AHMEDGARH</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>1326</v>
+        <v>1660</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>KUP</t>
+          <t>KARAM PATTI GRAIN MARKET</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>30.60582</v>
+        <v>30.2397029</v>
       </c>
       <c r="I81" t="n">
-        <v>75.87558</v>
+        <v>74.2953411</v>
       </c>
       <c r="J81" t="n">
-        <v>57</v>
+        <v>279</v>
       </c>
       <c r="K81" t="n">
-        <v>30.58822</v>
+        <v>30.175344</v>
       </c>
       <c r="L81" t="n">
-        <v>75.6722</v>
+        <v>74.178363</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -7863,7 +7863,7 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>866</v>
+        <v>401</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -7877,19 +7877,19 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>MALERKOTLA</t>
+          <t>FAZILKA</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>AHMEDGARH</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S81" t="n">
-        <v>30.458388</v>
+        <v>30.17081207</v>
       </c>
       <c r="T81" t="n">
-        <v>74.453514</v>
+        <v>74.18179719</v>
       </c>
       <c r="U81" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         </is>
       </c>
       <c r="V81" t="n">
-        <v>13140</v>
+        <v>1314.5</v>
       </c>
     </row>
     <row r="82">
@@ -7918,36 +7918,36 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>MALERKOTLA</t>
+          <t>SRI MUKTSAR SAHIB</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AHMEDGARH</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1326</v>
+        <v>1660</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>KUP</t>
+          <t>KARAM PATTI GRAIN MARKET</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>30.60582</v>
+        <v>30.2397029</v>
       </c>
       <c r="I82" t="n">
-        <v>75.87558</v>
+        <v>74.2953411</v>
       </c>
       <c r="J82" t="n">
-        <v>57</v>
+        <v>279</v>
       </c>
       <c r="K82" t="n">
-        <v>30.58822</v>
+        <v>30.175344</v>
       </c>
       <c r="L82" t="n">
-        <v>75.6722</v>
+        <v>74.178363</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>874</v>
+        <v>406</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
@@ -7969,19 +7969,19 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>MALERKOTLA</t>
+          <t>FAZILKA</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>AHMEDGARH</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S82" t="n">
-        <v>30.458388</v>
+        <v>30.16991135</v>
       </c>
       <c r="T82" t="n">
-        <v>74.453514</v>
+        <v>74.18230296</v>
       </c>
       <c r="U82" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
         </is>
       </c>
       <c r="V82" t="n">
-        <v>28460</v>
+        <v>52394.5</v>
       </c>
     </row>
     <row r="83">
@@ -8010,36 +8010,36 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>MALERKOTLA</t>
+          <t>TARN TARAN</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AHMEDGARH</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>1326</v>
+        <v>2153</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>KUP</t>
+          <t>KHALRA GRAIN MARKET</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>30.60582</v>
+        <v>31.3953454</v>
       </c>
       <c r="I83" t="n">
-        <v>75.87558</v>
+        <v>74.6222925</v>
       </c>
       <c r="J83" t="n">
-        <v>57</v>
+        <v>1948</v>
       </c>
       <c r="K83" t="n">
-        <v>30.58822</v>
+        <v>31.361236</v>
       </c>
       <c r="L83" t="n">
-        <v>75.6722</v>
+        <v>74.66727400000001</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>879</v>
+        <v>2</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
@@ -8061,19 +8061,19 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>MALERKOTLA</t>
+          <t>AMRITSAR</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>AHMEDGARH</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S83" t="n">
-        <v>30.458388</v>
+        <v>31.45335</v>
       </c>
       <c r="T83" t="n">
-        <v>74.453514</v>
+        <v>74.46541999999999</v>
       </c>
       <c r="U83" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         </is>
       </c>
       <c r="V83" t="n">
-        <v>2480</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="84">
@@ -8102,36 +8102,36 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>MALERKOTLA</t>
+          <t>TARN TARAN</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AHMEDGARH</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1327</v>
+        <v>2153</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>MAHOLI KALAN</t>
+          <t>KHALRA GRAIN MARKET</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>30.62411</v>
+        <v>31.3953454</v>
       </c>
       <c r="I84" t="n">
-        <v>75.75073</v>
+        <v>74.6222925</v>
       </c>
       <c r="J84" t="n">
-        <v>217</v>
+        <v>1948</v>
       </c>
       <c r="K84" t="n">
-        <v>30.51445</v>
+        <v>31.361236</v>
       </c>
       <c r="L84" t="n">
-        <v>74.89836</v>
+        <v>74.66727400000001</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>866</v>
+        <v>4</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
@@ -8153,19 +8153,19 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>MALERKOTLA</t>
+          <t>AMRITSAR</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>AHMEDGARH</t>
+          <t>Stor</t>
         </is>
       </c>
       <c r="S84" t="n">
-        <v>30.458388</v>
+        <v>31.45335</v>
       </c>
       <c r="T84" t="n">
-        <v>74.453514</v>
+        <v>74.46541999999999</v>
       </c>
       <c r="U84" t="inlineStr">
         <is>
@@ -8173,467 +8173,7 @@
         </is>
       </c>
       <c r="V84" t="n">
-        <v>59240</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Optimized</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>PC</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Haryana</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>MALERKOTLA</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AHMEDGARH</t>
-        </is>
-      </c>
-      <c r="F85" t="n">
-        <v>1328</v>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>MANAK HERI</t>
-        </is>
-      </c>
-      <c r="H85" t="n">
-        <v>30.58776</v>
-      </c>
-      <c r="I85" t="n">
-        <v>75.81787</v>
-      </c>
-      <c r="J85" t="n">
-        <v>216</v>
-      </c>
-      <c r="K85" t="n">
-        <v>30.5076194</v>
-      </c>
-      <c r="L85" t="n">
-        <v>74.958715</v>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>Depot</t>
-        </is>
-      </c>
-      <c r="N85" t="n">
-        <v>866</v>
-      </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>agah</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>Haryana</t>
-        </is>
-      </c>
-      <c r="Q85" t="inlineStr">
-        <is>
-          <t>MALERKOTLA</t>
-        </is>
-      </c>
-      <c r="R85" t="inlineStr">
-        <is>
-          <t>AHMEDGARH</t>
-        </is>
-      </c>
-      <c r="S85" t="n">
-        <v>30.458388</v>
-      </c>
-      <c r="T85" t="n">
-        <v>74.453514</v>
-      </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>Paddy</t>
-        </is>
-      </c>
-      <c r="V85" t="n">
-        <v>11670</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Optimized</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>PC</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Haryana</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>MALERKOTLA</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AHMEDGARH</t>
-        </is>
-      </c>
-      <c r="F86" t="n">
-        <v>1328</v>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>MANAK HERI</t>
-        </is>
-      </c>
-      <c r="H86" t="n">
-        <v>30.58776</v>
-      </c>
-      <c r="I86" t="n">
-        <v>75.81787</v>
-      </c>
-      <c r="J86" t="n">
-        <v>216</v>
-      </c>
-      <c r="K86" t="n">
-        <v>30.5076194</v>
-      </c>
-      <c r="L86" t="n">
-        <v>74.958715</v>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>Depot</t>
-        </is>
-      </c>
-      <c r="N86" t="n">
-        <v>880</v>
-      </c>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t>agah</t>
-        </is>
-      </c>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>Haryana</t>
-        </is>
-      </c>
-      <c r="Q86" t="inlineStr">
-        <is>
-          <t>MALERKOTLA</t>
-        </is>
-      </c>
-      <c r="R86" t="inlineStr">
-        <is>
-          <t>AHMEDGARH</t>
-        </is>
-      </c>
-      <c r="S86" t="n">
-        <v>30.458388</v>
-      </c>
-      <c r="T86" t="n">
-        <v>74.453514</v>
-      </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>Paddy</t>
-        </is>
-      </c>
-      <c r="V86" t="n">
-        <v>15360</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Optimized</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>PC</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Haryana</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>MALERKOTLA</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AHMEDGARH</t>
-        </is>
-      </c>
-      <c r="F87" t="n">
-        <v>1329</v>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>MOMNA BAD</t>
-        </is>
-      </c>
-      <c r="H87" t="n">
-        <v>30.669134</v>
-      </c>
-      <c r="I87" t="n">
-        <v>75.877723</v>
-      </c>
-      <c r="J87" t="n">
-        <v>678</v>
-      </c>
-      <c r="K87" t="n">
-        <v>30.633572</v>
-      </c>
-      <c r="L87" t="n">
-        <v>75.628421</v>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>Depot</t>
-        </is>
-      </c>
-      <c r="N87" t="n">
-        <v>877</v>
-      </c>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>agah</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>Haryana</t>
-        </is>
-      </c>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>MALERKOTLA</t>
-        </is>
-      </c>
-      <c r="R87" t="inlineStr">
-        <is>
-          <t>AHMEDGARH</t>
-        </is>
-      </c>
-      <c r="S87" t="n">
-        <v>30.458388</v>
-      </c>
-      <c r="T87" t="n">
-        <v>74.453514</v>
-      </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>Paddy</t>
-        </is>
-      </c>
-      <c r="V87" t="n">
-        <v>10530</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Optimized</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>PC</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Haryana</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>MALERKOTLA</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AHMEDGARH</t>
-        </is>
-      </c>
-      <c r="F88" t="n">
-        <v>1330</v>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>UMARPURA (NATHUMAJRA)</t>
-        </is>
-      </c>
-      <c r="H88" t="n">
-        <v>30.651445</v>
-      </c>
-      <c r="I88" t="n">
-        <v>75.890028</v>
-      </c>
-      <c r="J88" t="n">
-        <v>1225</v>
-      </c>
-      <c r="K88" t="n">
-        <v>30.5792101</v>
-      </c>
-      <c r="L88" t="n">
-        <v>75.30097960000001</v>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>Depot</t>
-        </is>
-      </c>
-      <c r="N88" t="n">
-        <v>872</v>
-      </c>
-      <c r="O88" t="inlineStr">
-        <is>
-          <t>agah</t>
-        </is>
-      </c>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t>Haryana</t>
-        </is>
-      </c>
-      <c r="Q88" t="inlineStr">
-        <is>
-          <t>MALERKOTLA</t>
-        </is>
-      </c>
-      <c r="R88" t="inlineStr">
-        <is>
-          <t>AHMEDGARH</t>
-        </is>
-      </c>
-      <c r="S88" t="n">
-        <v>30.458388</v>
-      </c>
-      <c r="T88" t="n">
-        <v>74.453514</v>
-      </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>Paddy</t>
-        </is>
-      </c>
-      <c r="V88" t="n">
-        <v>29640</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Optimized</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>PC</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Punjab</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>SRI MUKTSAR SAHIB</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Malout</t>
-        </is>
-      </c>
-      <c r="F89" t="n">
-        <v>1660</v>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>KARAM PATTI GRAIN MARKET</t>
-        </is>
-      </c>
-      <c r="H89" t="n">
-        <v>30.2397029</v>
-      </c>
-      <c r="I89" t="n">
-        <v>74.2953411</v>
-      </c>
-      <c r="J89" t="n">
-        <v>287</v>
-      </c>
-      <c r="K89" t="n">
-        <v>30.126927</v>
-      </c>
-      <c r="L89" t="n">
-        <v>74.161942</v>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>Depot</t>
-        </is>
-      </c>
-      <c r="N89" t="n">
-        <v>407</v>
-      </c>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t>agah</t>
-        </is>
-      </c>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>Punjab</t>
-        </is>
-      </c>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>FAZILKA</t>
-        </is>
-      </c>
-      <c r="R89" t="inlineStr">
-        <is>
-          <t>Abohar</t>
-        </is>
-      </c>
-      <c r="S89" t="n">
-        <v>30.126927</v>
-      </c>
-      <c r="T89" t="n">
-        <v>74.161942</v>
-      </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>Paddy</t>
-        </is>
-      </c>
-      <c r="V89" t="n">
-        <v>15621</v>
+        <v>150000</v>
       </c>
     </row>
   </sheetData>

--- a/pds_admin_Punjab_R/Backend/Backend/Tagging_Sheet_With_WB.xlsx
+++ b/pds_admin_Punjab_R/Backend/Backend/Tagging_Sheet_With_WB.xlsx
@@ -609,7 +609,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>AMRITSAR</t>
+          <t>Amritsar</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>AMRITSAR</t>
+          <t>Amritsar</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -5301,7 +5301,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -5669,7 +5669,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5761,7 +5761,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5945,7 +5945,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -6037,7 +6037,7 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>JALANDHAR</t>
+          <t>Jalandhar</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>MALERKOTLA</t>
+          <t>Malerkotla</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>MALERKOTLA</t>
+          <t>Malerkotla</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>MALERKOTLA</t>
+          <t>Malerkotla</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>MALERKOTLA</t>
+          <t>Malerkotla</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>MALERKOTLA</t>
+          <t>Malerkotla</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>MALERKOTLA</t>
+          <t>Malerkotla</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>MALERKOTLA</t>
+          <t>Malerkotla</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -6773,7 +6773,7 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>MALERKOTLA</t>
+          <t>Malerkotla</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -6865,7 +6865,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>MALERKOTLA</t>
+          <t>Malerkotla</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>MALERKOTLA</t>
+          <t>Malerkotla</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>MALERKOTLA</t>
+          <t>Malerkotla</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>MALERKOTLA</t>
+          <t>Malerkotla</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -7233,7 +7233,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>MALERKOTLA</t>
+          <t>Malerkotla</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>MALERKOTLA</t>
+          <t>Malerkotla</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>MALERKOTLA</t>
+          <t>Malerkotla</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>MALERKOTLA</t>
+          <t>Malerkotla</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>MALERKOTLA</t>
+          <t>Malerkotla</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>MALERKOTLA</t>
+          <t>Malerkotla</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>MALERKOTLA</t>
+          <t>Malerkotla</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -7969,7 +7969,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>FAZILKA</t>
+          <t>Fazilka</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>AMRITSAR</t>
+          <t>Amritsar</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>AMRITSAR</t>
+          <t>Amritsar</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
